--- a/MSTELevel.xlsx
+++ b/MSTELevel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b851c41abeb74cbb/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MathSaveTheEarth\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE1CFFA6-2530-4596-B0C7-499801DCBF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83BEB050-8FA3-4744-AD81-EC5C4BC3476E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>STAGE|1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -51,22 +50,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>PRINT|"우주선을 움직여 숫자를 먹고 적을 향해 발사하세요!"|2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PRINT|"HP가 높은 적은 +를 넣어 수식을 만들어 공격해 보세요."|2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PRINT|"이제 보스가 등장합니다. 더 긴 수식을 만들어 보세요."|2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>B(10)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>STAGE|END</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -83,7 +66,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ITEM|HR</t>
+    <t>PRINT|"HP가 높은 적은 +를 넣어 수식을 만들어 공격해 보세요."|3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRINT|"우주선을 움직여 숫자를 먹고 적을 향해 발사하세요!"|3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NUMBER|1, 2, 3, 4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRINT|"정확한 숫자를 맞추면 크리티컬 폭발이 일어납니다!"|3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRINT|"크리티컬 폭발은 주변의 다른 적에게도 타격을 줍니다."|3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRINT|"이제 보스가 등장합니다. 더 긴 수식을 만들어 보세요."|3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B(45)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -127,8 +134,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -144,10 +154,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -447,123 +453,249 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D8" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G12" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C14" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E18" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C25" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F27" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D31" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D41" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D8">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C42" s="1">
+        <v>3</v>
+      </c>
+      <c r="E42" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D45" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B9">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C46" s="1">
+        <v>4</v>
+      </c>
+      <c r="E46" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B47" s="1">
+        <v>4</v>
+      </c>
+      <c r="F47" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D50" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C51" s="1">
+        <v>5</v>
+      </c>
+      <c r="E51" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B52" s="1">
+        <v>5</v>
+      </c>
+      <c r="F52" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>5</v>
+      </c>
+      <c r="G53" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B56" s="1">
+        <v>6</v>
+      </c>
+      <c r="F56" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C57" s="1">
+        <v>6</v>
+      </c>
+      <c r="E57" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B58" s="1">
+        <v>6</v>
+      </c>
+      <c r="G58" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C59" s="1">
+        <v>6</v>
+      </c>
+      <c r="E59" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>6</v>
+      </c>
+      <c r="G60" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C61" s="1">
+        <v>6</v>
+      </c>
+      <c r="F61" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B70" s="1">
+        <v>10</v>
+      </c>
+      <c r="F70" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D71" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C17">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F19">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B22">
-        <v>5</v>
-      </c>
-      <c r="D22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/MSTELevel.xlsx
+++ b/MSTELevel.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MathSaveTheEarth\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83BEB050-8FA3-4744-AD81-EC5C4BC3476E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{E436DC4E-F3C0-43E9-A48C-5100F83C018E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
   <si>
     <t>STAGE|1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -78,19 +80,95 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>PRINT|"정확한 숫자를 맞추면 크리티컬 폭발이 일어납니다!"|3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PRINT|"크리티컬 폭발은 주변의 다른 적에게도 타격을 줍니다."|3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>PRINT|"이제 보스가 등장합니다. 더 긴 수식을 만들어 보세요."|3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>B(45)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STAGE|2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM|test_bgm_02.mp3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SYMBOL|+, ×</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRINT|"적의 대군단이 몰려옵니다!"|3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRINT|"어떤 적은 정확한 숫자를 맞춰야  파괴할 수 있습니다."|3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C(1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C(6)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C(12)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SYMBOL|+, ×, ×</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRINT|"소수는 +와 ×를 조합해서 만들 수 있습니다."|3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C(15)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C(20)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NUMBER|1, 2, 3, 4, 5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRINT|"지금부터  ×가 등장합니다.\n×를 활용해 더 강력한 수식을 만드세요!"|4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRINT|"정확한 숫자를 맞추면 크리티컬 폭발이 일어납니다!\n크리티컬 폭발은 주변의 다른 적에게도 타격을 줍니다."|3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FORCE{2, 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FORCE|3, 4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C(11)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FORCE|1, 1, 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B(55)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FORCE|2, 5, 1, 2, 5, 1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -134,10 +212,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -453,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
@@ -534,6 +615,9 @@
         <v>6</v>
       </c>
     </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+    </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F27" s="1">
         <v>5</v>
@@ -551,150 +635,526 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D38" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C39" s="1">
+        <v>3</v>
+      </c>
+      <c r="E39" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D42" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C43" s="1">
+        <v>4</v>
+      </c>
+      <c r="E43" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B44" s="1">
+        <v>4</v>
+      </c>
+      <c r="F44" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D47" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C48" s="1">
+        <v>5</v>
+      </c>
+      <c r="E48" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B49" s="1">
+        <v>5</v>
+      </c>
+      <c r="F49" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>5</v>
+      </c>
+      <c r="G50" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B53" s="1">
+        <v>6</v>
+      </c>
+      <c r="F53" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C54" s="1">
+        <v>6</v>
+      </c>
+      <c r="E54" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B55" s="1">
+        <v>6</v>
+      </c>
+      <c r="G55" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C56" s="1">
+        <v>6</v>
+      </c>
+      <c r="E56" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>6</v>
+      </c>
+      <c r="G57" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C58" s="1">
+        <v>6</v>
+      </c>
+      <c r="F58" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B67" s="1">
+        <v>10</v>
+      </c>
+      <c r="F67" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D68" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D41" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C42" s="1">
-        <v>3</v>
-      </c>
-      <c r="E42" s="1">
-        <v>3</v>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939BC4B4-D320-41F9-BACC-516C61336204}">
+  <dimension ref="A1:G84"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E10" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C12" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C17" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E20" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C29" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E34" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F43" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E44" s="1">
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D45" s="1">
-        <v>4</v>
+      <c r="D45" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C46" s="1">
-        <v>4</v>
-      </c>
-      <c r="E46" s="1">
-        <v>4</v>
+      <c r="A46" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B47" s="1">
-        <v>4</v>
-      </c>
-      <c r="F47" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D50" s="1">
-        <v>5</v>
+      <c r="C47" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B48" s="1">
+        <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C51" s="1">
-        <v>5</v>
-      </c>
-      <c r="E51" s="1">
-        <v>5</v>
+      <c r="A51" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B52" s="1">
-        <v>5</v>
-      </c>
-      <c r="F52" s="1">
-        <v>5</v>
+      <c r="A52" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="1">
-        <v>5</v>
-      </c>
-      <c r="G53" s="1">
-        <v>5</v>
+      <c r="A53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>2</v>
+      </c>
+      <c r="C55" s="1">
+        <v>2</v>
+      </c>
+      <c r="E55" s="1">
+        <v>2</v>
+      </c>
+      <c r="G55" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B56" s="1">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="D56" s="1">
+        <v>2</v>
       </c>
       <c r="F56" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>2</v>
+      </c>
       <c r="C57" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E57" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B58" s="1">
-        <v>6</v>
-      </c>
-      <c r="G58" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C59" s="1">
-        <v>6</v>
-      </c>
-      <c r="E59" s="1">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="G57" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="C60" s="1">
+        <v>3</v>
+      </c>
+      <c r="E60" s="1">
+        <v>3</v>
       </c>
       <c r="G60" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C61" s="1">
-        <v>6</v>
+      <c r="B61" s="1">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1">
+        <v>3</v>
       </c>
       <c r="F61" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B70" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>3</v>
+      </c>
+      <c r="C62" s="1">
+        <v>3</v>
+      </c>
+      <c r="E62" s="1">
+        <v>3</v>
+      </c>
+      <c r="G62" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>5</v>
+      </c>
+      <c r="C65" s="1">
+        <v>5</v>
+      </c>
+      <c r="E65" s="1">
+        <v>5</v>
+      </c>
+      <c r="G65" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B66" s="1">
+        <v>5</v>
+      </c>
+      <c r="D66" s="1">
+        <v>5</v>
+      </c>
+      <c r="F66" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>5</v>
+      </c>
+      <c r="C67" s="1">
+        <v>5</v>
+      </c>
+      <c r="E67" s="1">
+        <v>5</v>
+      </c>
+      <c r="G67" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>7</v>
+      </c>
+      <c r="C70" s="1">
+        <v>7</v>
+      </c>
+      <c r="E70" s="1">
+        <v>7</v>
+      </c>
+      <c r="G70" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B71" s="1">
+        <v>7</v>
+      </c>
+      <c r="D71" s="1">
+        <v>7</v>
+      </c>
+      <c r="F71" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>7</v>
+      </c>
+      <c r="C72" s="1">
+        <v>7</v>
+      </c>
+      <c r="E72" s="1">
+        <v>7</v>
+      </c>
+      <c r="G72" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F70" s="1">
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B80" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D71" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="1" t="s">
+      <c r="C80" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F80" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B81" s="1">
+        <v>10</v>
+      </c>
+      <c r="F81" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B82" s="1">
+        <v>10</v>
+      </c>
+      <c r="F82" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D83" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/MSTELevel.xlsx
+++ b/MSTELevel.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MathSaveTheEarth\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{E436DC4E-F3C0-43E9-A48C-5100F83C018E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB93455-69AE-4444-85E8-B5FA29E291A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="49">
   <si>
     <t>STAGE|1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -170,23 +170,71 @@
   <si>
     <t>FORCE|2, 5, 1, 2, 5, 1</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STAGE|3</t>
+  </si>
+  <si>
+    <t>BGM|test_bgm_03.mp3</t>
+  </si>
+  <si>
+    <t>NUMBER|1, 2, 3, 4, 5, 6, 7, 8, 9, 10</t>
+  </si>
+  <si>
+    <t>SYMBOL|+, ×, -, ÷</t>
+  </si>
+  <si>
+    <t>PRINT|"지금부터   -와  ÷가 등장합니다."|4</t>
+  </si>
+  <si>
+    <t>`</t>
+  </si>
+  <si>
+    <t>가족관계증명서, 외국인등록증 은평지사로</t>
+  </si>
+  <si>
+    <t>건강보험지역가입자가격취득변동신고서</t>
+  </si>
+  <si>
+    <t>불광역 근처</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1668-0159 </t>
+  </si>
+  <si>
+    <t>C(10)</t>
+  </si>
+  <si>
+    <t>PRINT|"수송선을 파괴하면 아이템을 얻을 수 있어요."|4</t>
+  </si>
+  <si>
+    <t>ITEM(EB)</t>
+  </si>
+  <si>
+    <t>PRINT|"E는 10과 ×를 잔뜩 만들어냅니다."|4</t>
+  </si>
+  <si>
+    <t>PRINT|"이제 보스가 등장합니다. 아이템을 사용해 물리치세요."|3</t>
+  </si>
+  <si>
+    <t>B(1000000)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -222,7 +270,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -238,7 +286,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -535,115 +583,115 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G69"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="D8" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="B10" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="G12" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="C14" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="E18" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6">
       <c r="C25" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6">
       <c r="F27" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6">
       <c r="B29" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6">
       <c r="D31" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6">
       <c r="A35" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6">
       <c r="D38" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6">
       <c r="C39" s="1">
         <v>3</v>
       </c>
@@ -651,12 +699,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6">
       <c r="D42" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6">
       <c r="C43" s="1">
         <v>4</v>
       </c>
@@ -664,7 +712,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6">
       <c r="B44" s="1">
         <v>4</v>
       </c>
@@ -672,12 +720,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6">
       <c r="D47" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6">
       <c r="C48" s="1">
         <v>5</v>
       </c>
@@ -685,7 +733,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="B49" s="1">
         <v>5</v>
       </c>
@@ -693,7 +741,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -701,7 +749,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7">
       <c r="B53" s="1">
         <v>6</v>
       </c>
@@ -709,7 +757,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7">
       <c r="C54" s="1">
         <v>6</v>
       </c>
@@ -717,7 +765,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7">
       <c r="B55" s="1">
         <v>6</v>
       </c>
@@ -725,7 +773,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7">
       <c r="C56" s="1">
         <v>6</v>
       </c>
@@ -733,7 +781,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -741,7 +789,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7">
       <c r="C58" s="1">
         <v>6</v>
       </c>
@@ -749,17 +797,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7">
       <c r="A63" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7">
       <c r="A64" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6">
       <c r="B67" s="1">
         <v>10</v>
       </c>
@@ -767,12 +815,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6">
       <c r="D68" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6">
       <c r="A69" s="1" t="s">
         <v>3</v>
       </c>
@@ -786,147 +834,147 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939BC4B4-D320-41F9-BACC-516C61336204}">
   <dimension ref="A1:G84"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="E10" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5">
       <c r="C12" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="E14" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="C17" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="E20" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5">
       <c r="A26" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5">
       <c r="C29" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6">
       <c r="A33" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6">
       <c r="E34" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6">
       <c r="A39" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6">
       <c r="A40" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6">
       <c r="F43" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6">
       <c r="E44" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6">
       <c r="D45" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6">
       <c r="A46" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6">
       <c r="C47" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6">
       <c r="B48" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7">
       <c r="A51" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7">
       <c r="A52" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7">
       <c r="A53" s="1" t="s">
         <v>17</v>
       </c>
@@ -949,7 +997,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7">
       <c r="A55" s="1">
         <v>2</v>
       </c>
@@ -963,7 +1011,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7">
       <c r="B56" s="1">
         <v>2</v>
       </c>
@@ -974,7 +1022,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7">
       <c r="A57" s="1">
         <v>2</v>
       </c>
@@ -988,7 +1036,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7">
       <c r="A60" s="1">
         <v>3</v>
       </c>
@@ -1002,7 +1050,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7">
       <c r="B61" s="1">
         <v>3</v>
       </c>
@@ -1013,7 +1061,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7">
       <c r="A62" s="1">
         <v>3</v>
       </c>
@@ -1027,7 +1075,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7">
       <c r="A65" s="1">
         <v>5</v>
       </c>
@@ -1041,7 +1089,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7">
       <c r="B66" s="1">
         <v>5</v>
       </c>
@@ -1052,7 +1100,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7">
       <c r="A67" s="1">
         <v>5</v>
       </c>
@@ -1066,7 +1114,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7">
       <c r="A70" s="1">
         <v>7</v>
       </c>
@@ -1080,7 +1128,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7">
       <c r="B71" s="1">
         <v>7</v>
       </c>
@@ -1091,7 +1139,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7">
       <c r="A72" s="1">
         <v>7</v>
       </c>
@@ -1105,17 +1153,17 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7">
       <c r="A76" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7">
       <c r="A77" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7">
       <c r="B80" s="1">
         <v>10</v>
       </c>
@@ -1132,7 +1180,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6">
       <c r="B81" s="1">
         <v>10</v>
       </c>
@@ -1140,7 +1188,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6">
       <c r="B82" s="1">
         <v>10</v>
       </c>
@@ -1148,12 +1196,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6">
       <c r="D83" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6">
       <c r="A84" s="1" t="s">
         <v>3</v>
       </c>
@@ -1162,4 +1210,412 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51B9BE69-4CCA-4A23-B101-3EDF53216623}">
+  <dimension ref="A1:G113"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5">
+      <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="16.5">
+      <c r="A2" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="16.5">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16.5">
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16.5">
+      <c r="A5" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="16.5">
+      <c r="A7" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="16.5">
+      <c r="D10" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="B11" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16.5">
+      <c r="F12" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16.5"/>
+    <row r="14" spans="1:7">
+      <c r="G14" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="16.5">
+      <c r="C15" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="E16" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="B18" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="16.5">
+      <c r="D19" s="1">
+        <v>11</v>
+      </c>
+      <c r="G19" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="16.5">
+      <c r="A22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="16.5"/>
+    <row r="26" spans="1:7">
+      <c r="B26" s="1">
+        <v>14</v>
+      </c>
+      <c r="F26" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="16.5">
+      <c r="D27" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="C28" s="1">
+        <v>23</v>
+      </c>
+      <c r="E28" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="16.5">
+      <c r="B29" s="1">
+        <v>22</v>
+      </c>
+      <c r="F29" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="16.5">
+      <c r="C30" s="1">
+        <v>10</v>
+      </c>
+      <c r="E30" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="16.5">
+      <c r="D31" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="E34" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="16.5"/>
+    <row r="36" spans="1:7" ht="16.5"/>
+    <row r="37" spans="1:7" ht="16.5"/>
+    <row r="39" spans="1:7">
+      <c r="A39" s="1">
+        <v>5</v>
+      </c>
+      <c r="C39" s="1">
+        <v>7</v>
+      </c>
+      <c r="E39" s="1">
+        <v>11</v>
+      </c>
+      <c r="G39" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="1">
+        <v>29</v>
+      </c>
+      <c r="C41" s="1">
+        <v>23</v>
+      </c>
+      <c r="E41" s="1">
+        <v>19</v>
+      </c>
+      <c r="G41" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="16.5"/>
+    <row r="43" spans="1:7" ht="16.5">
+      <c r="A43" s="1">
+        <v>31</v>
+      </c>
+      <c r="C43" s="1">
+        <v>37</v>
+      </c>
+      <c r="E43" s="1">
+        <v>41</v>
+      </c>
+      <c r="G43" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="16.5"/>
+    <row r="47" spans="1:7" ht="16.5"/>
+    <row r="48" spans="1:7" ht="16.5">
+      <c r="A48" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="16.5">
+      <c r="A49" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="16.5">
+      <c r="A50" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="16.5">
+      <c r="A51" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="G52" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="G53" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="16.5">
+      <c r="A54" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="16.5"/>
+    <row r="56" spans="1:7" ht="16.5"/>
+    <row r="57" spans="1:7">
+      <c r="A57" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="16.5"/>
+    <row r="59" spans="1:7" ht="16.5">
+      <c r="A59" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="16.5"/>
+    <row r="62" spans="1:7">
+      <c r="D62" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="16.5"/>
+    <row r="64" spans="1:7" ht="16.5">
+      <c r="A64" s="2"/>
+      <c r="B64" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="16.5"/>
+    <row r="66" spans="1:7">
+      <c r="F66" s="1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="16.5">
+      <c r="C68" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="16.5"/>
+    <row r="70" spans="1:7" ht="16.5"/>
+    <row r="71" spans="1:7" ht="16.5"/>
+    <row r="72" spans="1:7">
+      <c r="A72" s="1">
+        <v>10</v>
+      </c>
+      <c r="B72" s="1">
+        <v>10</v>
+      </c>
+      <c r="C72" s="1">
+        <v>10</v>
+      </c>
+      <c r="D72" s="1">
+        <v>10</v>
+      </c>
+      <c r="E72" s="1">
+        <v>10</v>
+      </c>
+      <c r="F72" s="1">
+        <v>10</v>
+      </c>
+      <c r="G72" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="16.5">
+      <c r="A75" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="16.5">
+      <c r="A76" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="D78" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="16.5"/>
+    <row r="80" spans="1:7" ht="16.5"/>
+    <row r="81" spans="1:6" ht="16.5">
+      <c r="B81" s="1">
+        <v>999999</v>
+      </c>
+      <c r="F81" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="16.5">
+      <c r="B82" s="1">
+        <v>999999</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F82" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="16.5"/>
+    <row r="84" spans="1:6">
+      <c r="A84" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/MSTELevel.xlsx
+++ b/MSTELevel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MathSaveTheEarth\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB93455-69AE-4444-85E8-B5FA29E291A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1E6A3C-DD96-4D82-8AFC-942401DF2B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="53">
   <si>
     <t>STAGE|1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -181,9 +181,6 @@
     <t>NUMBER|1, 2, 3, 4, 5, 6, 7, 8, 9, 10</t>
   </si>
   <si>
-    <t>SYMBOL|+, ×, -, ÷</t>
-  </si>
-  <si>
     <t>PRINT|"지금부터   -와  ÷가 등장합니다."|4</t>
   </si>
   <si>
@@ -217,7 +214,22 @@
     <t>PRINT|"이제 보스가 등장합니다. 아이템을 사용해 물리치세요."|3</t>
   </si>
   <si>
-    <t>B(1000000)</t>
+    <t>SYMBOL|+,-,+, ×, -,+,×, ÷,×</t>
+  </si>
+  <si>
+    <t>FORCE| 4, 5</t>
+  </si>
+  <si>
+    <t>FORCE| 10,10</t>
+  </si>
+  <si>
+    <t>FORCE| 3, 5, 6, 10</t>
+  </si>
+  <si>
+    <t>FORCE| 4, 5,8, 10</t>
+  </si>
+  <si>
+    <t>B(10000)</t>
   </si>
 </sst>
 </file>
@@ -1214,405 +1226,424 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51B9BE69-4CCA-4A23-B101-3EDF53216623}">
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.5">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="16.5">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.5">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="16.5">
-      <c r="A4" s="1" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.5">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:7">
+      <c r="A5" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.5">
-      <c r="A7" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="16.5">
+    <row r="10" spans="1:7">
       <c r="D10" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="B11" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="16.5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="F12" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.5"/>
     <row r="14" spans="1:7">
       <c r="G14" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.5">
+    <row r="15" spans="1:7">
       <c r="C15" s="1">
         <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
       <c r="E16" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:6">
       <c r="B18" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.5">
+    <row r="19" spans="1:6">
       <c r="D19" s="1">
         <v>11</v>
       </c>
-      <c r="G19" s="1">
+      <c r="F19" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.5">
-      <c r="A22" s="1" t="s">
-        <v>38</v>
+    <row r="22" spans="1:6">
+      <c r="A22" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="C22" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.5"/>
-    <row r="26" spans="1:7">
-      <c r="B26" s="1">
-        <v>14</v>
-      </c>
-      <c r="F26" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="16.5">
-      <c r="D27" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="C28" s="1">
-        <v>23</v>
-      </c>
-      <c r="E28" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="16.5">
-      <c r="B29" s="1">
-        <v>22</v>
-      </c>
-      <c r="F29" s="1">
+    <row r="27" spans="1:6">
+      <c r="B27" s="1">
+        <v>7</v>
+      </c>
+      <c r="F27" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="D29" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="C31" s="1">
+        <v>12</v>
+      </c>
+      <c r="E31" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="B32" s="1">
+        <v>13</v>
+      </c>
+      <c r="D32" s="1">
+        <v>20</v>
+      </c>
+      <c r="F32" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.5">
-      <c r="C30" s="1">
-        <v>10</v>
-      </c>
-      <c r="E30" s="1">
+    <row r="33" spans="1:7">
+      <c r="C33" s="1">
+        <v>10</v>
+      </c>
+      <c r="E33" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.5">
-      <c r="D31" s="1">
+    <row r="34" spans="1:7">
+      <c r="D34" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="C41" s="1">
+        <v>5</v>
+      </c>
+      <c r="E41" s="1">
+        <v>30</v>
+      </c>
+      <c r="G41" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="D42" s="1">
+        <v>28</v>
+      </c>
+      <c r="F42" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="E43" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
-      <c r="E34" s="1">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="16.5"/>
-    <row r="36" spans="1:7" ht="16.5"/>
-    <row r="37" spans="1:7" ht="16.5"/>
-    <row r="39" spans="1:7">
-      <c r="A39" s="1">
-        <v>5</v>
-      </c>
-      <c r="C39" s="1">
+    <row r="45" spans="1:7">
+      <c r="B45" s="1">
+        <v>26</v>
+      </c>
+      <c r="D45" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="2">
+        <v>37</v>
+      </c>
+      <c r="C46" s="1">
+        <v>40</v>
+      </c>
+      <c r="E46" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="B48" s="1">
         <v>7</v>
       </c>
-      <c r="E39" s="1">
-        <v>11</v>
-      </c>
-      <c r="G39" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="1">
-        <v>29</v>
-      </c>
-      <c r="C41" s="1">
-        <v>23</v>
-      </c>
-      <c r="E41" s="1">
-        <v>19</v>
-      </c>
-      <c r="G41" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="16.5"/>
-    <row r="43" spans="1:7" ht="16.5">
-      <c r="A43" s="1">
-        <v>31</v>
-      </c>
-      <c r="C43" s="1">
-        <v>37</v>
-      </c>
-      <c r="E43" s="1">
+      <c r="D48" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="G56" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="G57" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="D66" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="B68" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="C69" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="F70" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="C72" s="1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="2">
+        <v>10</v>
+      </c>
+      <c r="B76" s="1">
+        <v>10</v>
+      </c>
+      <c r="C76" s="1">
+        <v>10</v>
+      </c>
+      <c r="D76" s="1">
+        <v>10</v>
+      </c>
+      <c r="E76" s="1">
+        <v>10</v>
+      </c>
+      <c r="F76" s="1">
+        <v>10</v>
+      </c>
+      <c r="G76" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="D82" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="B85" s="1">
+        <v>9999</v>
+      </c>
+      <c r="F85" s="1">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="B86" s="1">
+        <v>9999</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F86" s="1">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="G87" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="G43" s="1">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="16.5"/>
-    <row r="47" spans="1:7" ht="16.5"/>
-    <row r="48" spans="1:7" ht="16.5">
-      <c r="A48" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="16.5">
-      <c r="A49" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="16.5">
-      <c r="A50" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="16.5">
-      <c r="A51" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="G52" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="G53" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="16.5">
-      <c r="A54" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="16.5"/>
-    <row r="56" spans="1:7" ht="16.5"/>
-    <row r="57" spans="1:7">
-      <c r="A57" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="16.5"/>
-    <row r="59" spans="1:7" ht="16.5">
-      <c r="A59" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="16.5"/>
-    <row r="62" spans="1:7">
-      <c r="D62" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="16.5"/>
-    <row r="64" spans="1:7" ht="16.5">
-      <c r="A64" s="2"/>
-      <c r="B64" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="16.5"/>
-    <row r="66" spans="1:7">
-      <c r="F66" s="1">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="16.5">
-      <c r="C68" s="1">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="16.5"/>
-    <row r="70" spans="1:7" ht="16.5"/>
-    <row r="71" spans="1:7" ht="16.5"/>
-    <row r="72" spans="1:7">
-      <c r="A72" s="1">
-        <v>10</v>
-      </c>
-      <c r="B72" s="1">
-        <v>10</v>
-      </c>
-      <c r="C72" s="1">
-        <v>10</v>
-      </c>
-      <c r="D72" s="1">
-        <v>10</v>
-      </c>
-      <c r="E72" s="1">
-        <v>10</v>
-      </c>
-      <c r="F72" s="1">
-        <v>10</v>
-      </c>
-      <c r="G72" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="16.5">
-      <c r="A75" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="16.5">
-      <c r="A76" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="D78" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="16.5"/>
-    <row r="80" spans="1:7" ht="16.5"/>
-    <row r="81" spans="1:6" ht="16.5">
-      <c r="B81" s="1">
-        <v>999999</v>
-      </c>
-      <c r="F81" s="1">
-        <v>999999</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="16.5">
-      <c r="B82" s="1">
-        <v>999999</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F82" s="1">
-        <v>999999</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="16.5"/>
-    <row r="84" spans="1:6">
-      <c r="A84" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1">
-      <c r="A112" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
